--- a/Compititor's_Price/Unilin_Prices/Unilin_Prices_10-09-2026.xlsx
+++ b/Compititor's_Price/Unilin_Prices/Unilin_Prices_10-09-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Unilin_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{830A666B-4608-4BA0-91D8-D3ADDD66E40F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4DFFB25-111B-4E15-A2BF-9EDFB5354A81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31965" yWindow="2925" windowWidth="21600" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1095" yWindow="1740" windowWidth="21600" windowHeight="10890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -94,7 +94,7 @@
     <t>Unilin Thin-R PIR 30mm x 2.4m x 1.2m</t>
   </si>
   <si>
-    <t>£17.37</t>
+    <t>£17.29</t>
   </si>
   <si>
     <t>£26.51</t>
@@ -115,7 +115,7 @@
     <t>Unilin Thin-R PIR 40mm x 2.4m x 1.2m</t>
   </si>
   <si>
-    <t>£20.83</t>
+    <t>£21.40</t>
   </si>
   <si>
     <t>£30.61</t>
@@ -178,7 +178,7 @@
     <t>Unilin Thin-R PIR 70mm x 2.4m x 1.2m</t>
   </si>
   <si>
-    <t>£31.00</t>
+    <t>£30.49</t>
   </si>
   <si>
     <t>£46.44</t>
@@ -199,7 +199,7 @@
     <t>Unilin Thin-R PIR 75mm x 2.4m x 1.2m</t>
   </si>
   <si>
-    <t>£29.49</t>
+    <t>£29.99</t>
   </si>
   <si>
     <t>£48.57</t>
@@ -220,7 +220,7 @@
     <t>Unilin Thin-R PIR 80mm x 2.4m x 1.2m</t>
   </si>
   <si>
-    <t>£34.09</t>
+    <t>£34.08</t>
   </si>
   <si>
     <t>£53.33</t>
@@ -298,7 +298,7 @@
     <t>Unilin Thin-R PIR 120mm x 2.4m x 1.2m</t>
   </si>
   <si>
-    <t>£45.79</t>
+    <t>£48.52</t>
   </si>
   <si>
     <t>£73.79</t>
@@ -331,7 +331,7 @@
     <t>Unilin Thin-R PIR 130mm x 2.4m x 1.2m</t>
   </si>
   <si>
-    <t>£55.79</t>
+    <t>£55.75</t>
   </si>
   <si>
     <t>£83.83</t>
@@ -352,7 +352,7 @@
     <t>Unilin Thin-R PIR 140mm x 2.4m x 1.2m</t>
   </si>
   <si>
-    <t>£57.10</t>
+    <t>£59.00</t>
   </si>
   <si>
     <t>£89.07</t>
